--- a/artfynd/A 33548-2023 artfynd.xlsx
+++ b/artfynd/A 33548-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33548-2023 artfynd.xlsx
+++ b/artfynd/A 33548-2023 artfynd.xlsx
@@ -832,7 +832,7 @@
         <v>111170990</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>111160737</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>111170460</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>111170660</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>111170565</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>111216085</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>111227320</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>111227901</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>111227586</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>111227944</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>111221122</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>111227666</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>111299300</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>111362562</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>

--- a/artfynd/A 33548-2023 artfynd.xlsx
+++ b/artfynd/A 33548-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AZ56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -821,6 +826,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111171323</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -971,6 +981,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111171761</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1120,6 +1135,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111176375</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1265,6 +1285,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111180652</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1406,6 +1431,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111221658</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1547,6 +1577,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111358214</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1688,6 +1723,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111358455</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1829,6 +1869,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111358524</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1970,6 +2015,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111358759</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2086,6 +2136,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111215908</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2212,6 +2267,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111357840</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2322,6 +2382,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111161755</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2463,6 +2528,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111219987</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2604,6 +2674,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111221491</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2745,6 +2820,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111355912</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2864,6 +2944,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111326228</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2988,6 +3073,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111160737</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3114,6 +3204,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111170460</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3244,6 +3339,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111170565</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3374,6 +3474,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111170660</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3504,6 +3609,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111170990</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3649,6 +3759,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111216085</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3779,6 +3894,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111216465</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3909,6 +4029,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111216533</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4039,6 +4164,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111216573</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4184,6 +4314,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111220661</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4314,6 +4449,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111221072</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4444,6 +4584,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111221122</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4589,6 +4734,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111227320</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4734,6 +4884,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111227586</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4864,6 +5019,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111227666</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4994,6 +5154,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111227901</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5124,6 +5289,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111227944</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5254,6 +5424,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111299300</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5384,6 +5559,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111362562</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5514,6 +5694,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111366515</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5656,6 +5841,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111221775</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5794,6 +5984,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111221813</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5903,6 +6098,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111326259</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -6023,6 +6223,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111326210</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6155,6 +6360,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111216742</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6291,6 +6501,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111366200</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6423,6 +6638,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111366550</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6558,6 +6778,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111170360</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6686,6 +6911,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111162475</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6812,6 +7042,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111170156</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6939,6 +7174,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111358288</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -7074,6 +7314,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111217438</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -7201,6 +7446,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111357675</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7328,6 +7578,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111357794</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7458,6 +7713,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111357955</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7585,6 +7845,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111358171</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7712,6 +7977,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111358662</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7829,6 +8099,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111358801</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7960,8 +8235,70 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111357523</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>